--- a/docs/downloads/经营分_津河省区__秦皇岛片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__秦皇岛片区_2026-10-19.xlsx
@@ -12,7 +12,7 @@
     <sheet name="匹配异常" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -771,17 +771,17 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>6601145441214023683</t>
+          <t>6601135946203138055</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>锦江之星秦皇岛燕山大学酒店</t>
+          <t>锦江之星(秦皇岛河北大街太阳城店)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛燕山大学酒店)</t>
+          <t>锦江之星(秦皇岛河北大街太阳城店)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I3" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -813,13 +813,13 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
         <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
         <v>30</v>
@@ -852,36 +852,32 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>秦皇岛市</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>6601148871122880515</t>
+          <t>6601145441214023683</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>喆啡酒店秦皇岛火车站万达广场店</t>
+          <t>锦江之星秦皇岛燕山大学酒店</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>喆啡酒店(秦皇岛火车站万达广场店)</t>
+          <t>锦江之星(秦皇岛燕山大学酒店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -907,13 +903,13 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>20</v>
@@ -947,17 +943,17 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6601205747747407885</t>
+          <t>6601148871122880515</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7天酒店（昌黎科技师范学院店）</t>
+          <t>喆啡酒店秦皇岛火车站万达广场店</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7天连锁酒店(昌黎碣阳大街店)</t>
+          <t>喆啡酒店(秦皇岛火车站万达广场店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -966,14 +962,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I5" t="n">
-        <v>-25</v>
+        <v>-22</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -1001,7 +997,7 @@
         <v>30</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
         <v>20</v>
@@ -1028,36 +1024,40 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>秦皇岛市</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>6854660969004632064</t>
+          <t>6601205747747407885</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>希岸酒店山海关老龙头浴场店</t>
+          <t>7天酒店（昌黎科技师范学院店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>希岸酒店(山海关老龙头浴场店)</t>
+          <t>7天连锁酒店(昌黎碣阳大街店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>-25</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1067,7 +1067,7 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
@@ -1085,7 +1085,7 @@
         <v>30</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="n">
         <v>20</v>
@@ -1115,17 +1115,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7504898891796465715</t>
+          <t>6854660969004632064</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>维也纳酒店(秦皇岛北戴河仙螺岛宁海道店)</t>
+          <t>希岸酒店山海关老龙头浴场店</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>维也纳酒店(秦皇岛北戴河仙螺岛宁海道店)</t>
+          <t>希岸酒店(山海关老龙头浴场店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1137,7 +1137,7 @@
         <v>67</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -1163,7 +1163,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1196,24 +1196,20 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>秦皇岛市</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6601142577448093710</t>
+          <t>7504898891796465715</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>喆啡酒店（秦皇岛人民公园广场店）</t>
+          <t>维也纳酒店(秦皇岛北戴河仙螺岛宁海道店)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>喆·啡酒店(人民公园店)</t>
+          <t>维也纳酒店(秦皇岛北戴河仙螺岛宁海道店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1222,14 +1218,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I8" t="n">
-        <v>-15</v>
+        <v>12</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1257,7 +1253,7 @@
         <v>30</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="n">
         <v>20</v>
@@ -1291,17 +1287,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6601163368889845767</t>
+          <t>6601142577448093710</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>麗枫酒店·秦皇岛火车站万达广场店</t>
+          <t>喆啡酒店（秦皇岛人民公园广场店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>丽枫酒店(秦皇岛迎宾路火车站店)</t>
+          <t>喆·啡酒店(人民公园店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1310,14 +1306,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I9" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1327,19 +1323,19 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O9" t="n">
+        <v>20</v>
+      </c>
+      <c r="P9" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>30</v>
-      </c>
-      <c r="O9" t="n">
-        <v>30</v>
-      </c>
-      <c r="P9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1379,43 +1375,43 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6724197542428559373</t>
+          <t>7590976773005772834</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>喆啡酒店（秦皇岛海港太阳城文化路店）</t>
+          <t>凯里亚德酒店(秦皇岛茂业天地燕山大学店)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>喆啡酒店(秦皇岛海港太阳城文化路店)</t>
+          <t>凯里亚德酒店(秦皇岛茂业天地燕山大学店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
@@ -1433,7 +1429,7 @@
         <v>30</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="n">
         <v>20</v>
@@ -1460,20 +1456,24 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>秦皇岛市</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6997902425902286880</t>
+          <t>6601163368889845767</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（河北秦皇岛北戴河店）</t>
+          <t>麗枫酒店·秦皇岛火车站万达广场店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(北戴河店)</t>
+          <t>丽枫酒店(秦皇岛迎宾路火车站店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1482,36 +1482,36 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I11" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>稳房源,拿收益</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>稳房源,提质量,拿收益</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" t="n">
-        <v>17</v>
-      </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1551,33 +1551,33 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7525679409429547023</t>
+          <t>6724197542428559373</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳酒店(秦皇岛金梦海湾秦皇之眼店)</t>
+          <t>喆啡酒店（秦皇岛海港太阳城文化路店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳酒店(秦皇岛金梦海湾秦皇之眼店)</t>
+          <t>喆啡酒店(秦皇岛海港太阳城文化路店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>77</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1587,7 +1587,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
@@ -1605,7 +1605,7 @@
         <v>30</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="n">
         <v>20</v>
@@ -1632,24 +1632,20 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>秦皇岛市</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7337172376020322316</t>
+          <t>6997902425902286880</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(秦皇岛燕山大学店)</t>
+          <t>维也纳3好酒店（河北秦皇岛北戴河店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(祁连山南路店)</t>
+          <t>维也纳3好酒店(北戴河店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1658,10 +1654,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1675,7 +1671,7 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
@@ -1720,36 +1716,40 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>秦皇岛市</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6601129048246585358</t>
+          <t>7525679409429547023</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>麗枫酒店·北戴河老虎石鸽子窝公园店</t>
+          <t>维也纳酒店(秦皇岛金梦海湾秦皇之眼店)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>麗枫酒店(北戴河老虎石店)</t>
+          <t>维也纳酒店(秦皇岛金梦海湾秦皇之眼店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1765,19 +1765,19 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="n">
         <v>20</v>
@@ -1811,37 +1811,37 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7451115976025704498</t>
+          <t>7337172376020322316</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>麗枫酒店秦皇岛抚宁健康大街店</t>
+          <t>维也纳智好酒店(秦皇岛燕山大学店)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>丽枫酒店(秦皇岛抚宁健康大街店)</t>
+          <t>维也纳智好酒店(祁连山南路店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1892,24 +1892,20 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>秦皇岛市</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6800946428765079556</t>
+          <t>7233255670936504380</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7天优品秦皇岛卢龙县政府兴龙广缘店</t>
+          <t>非繁城品酒店(北戴河老虎石店)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7天优品酒店(卢龙汽车站永旺大街店)</t>
+          <t>非繁城品酒店(北戴河老虎石店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1918,14 +1914,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1935,13 +1931,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -1983,17 +1979,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601140182064302083</t>
+          <t>6601129048246585358</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>锦江之星秦皇岛东山浴场西港花园店</t>
+          <t>麗枫酒店·北戴河老虎石鸽子窝公园店</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛东山浴场西港花园酒店)</t>
+          <t>麗枫酒店(北戴河老虎石店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2002,14 +1998,14 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2019,19 +2015,19 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2071,17 +2067,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7480089331252594714</t>
+          <t>7451115976025704498</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（秦皇岛昌黎店）</t>
+          <t>麗枫酒店秦皇岛抚宁健康大街店</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(昌黎店)</t>
+          <t>丽枫酒店(秦皇岛抚宁健康大街店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2090,18 +2086,18 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
         <v>10</v>
@@ -2159,17 +2155,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7599127059969640483</t>
+          <t>6800946428765079556</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳酒店（秦皇岛开发区燕山大学未来中心店）</t>
+          <t>7天优品秦皇岛卢龙县政府兴龙广缘店</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳酒店(未来中心店)</t>
+          <t>7天优品酒店(卢龙汽车站永旺大街店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2178,10 +2174,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2195,7 +2191,7 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
@@ -2240,24 +2236,20 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>秦皇岛市</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6659401537346996238</t>
+          <t>6601140182064302083</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>锦江之星秦皇岛昌黎酒店</t>
+          <t>锦江之星秦皇岛东山浴场西港花园店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛昌黎店)</t>
+          <t>锦江之星(秦皇岛东山浴场西港花园酒店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2266,7 +2258,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2283,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2295,7 +2287,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2335,17 +2327,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7507807387181385765</t>
+          <t>7480089331252594714</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>维也纳酒店（秦皇岛北戴河老虎石店）</t>
+          <t>维也纳国际酒店（秦皇岛昌黎店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>维也纳酒店(秦皇岛市北戴河店)</t>
+          <t>维也纳国际酒店(昌黎店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2354,7 +2346,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2377,7 +2369,7 @@
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
@@ -2423,17 +2415,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7369817645204146216</t>
+          <t>7599127059969640483</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>非繁城品酒店·秦皇岛火车站万达世纪港湾店</t>
+          <t>维也纳酒店（秦皇岛开发区燕山大学未来中心店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>非繁城品酒店(秦皇岛火车站万达世纪港湾店)</t>
+          <t>维也纳酒店(未来中心店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2442,7 +2434,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2465,7 +2457,7 @@
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -2511,17 +2503,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7598771935769528354</t>
+          <t>6659401537346996238</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>锦江之星秦皇岛开发区高速口店</t>
+          <t>锦江之星秦皇岛昌黎酒店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛开发区高速路口店)</t>
+          <t>锦江之星(秦皇岛昌黎店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2530,18 +2522,18 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
@@ -2559,7 +2551,7 @@
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2599,26 +2591,26 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6601186669309724675</t>
+          <t>7507807387181385765</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7天酒店秦皇岛东北大学秦皇小巷店</t>
+          <t>维也纳酒店（秦皇岛北戴河老虎石店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7天连锁酒店(秦皇岛东北大学珠江道店)</t>
+          <t>维也纳酒店(秦皇岛市北戴河店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2635,19 +2627,19 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
+        <v>22</v>
+      </c>
+      <c r="N24" t="n">
+        <v>30</v>
+      </c>
+      <c r="O24" t="n">
         <v>25</v>
       </c>
-      <c r="N24" t="n">
-        <v>30</v>
-      </c>
-      <c r="O24" t="n">
-        <v>20</v>
-      </c>
       <c r="P24" t="n">
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2687,17 +2679,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7379862818146748457</t>
+          <t>7369817645204146216</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IU酒店(秦皇岛抚宁区新大集市场店)</t>
+          <t>非繁城品酒店·秦皇岛火车站万达世纪港湾店</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>iu酒店(抚宁新大集市场店)</t>
+          <t>非繁城品酒店(秦皇岛火车站万达世纪港湾店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2706,7 +2698,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2723,7 +2715,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
@@ -2768,46 +2760,50 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>秦皇岛市</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7555530999078062132</t>
+          <t>7598771935769528354</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>喆啡酒店（山海关火车站天下第一关古城店）</t>
+          <t>锦江之星秦皇岛开发区高速口店</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>喆啡酒店(山海关火车站天下第一关古城店)</t>
+          <t>锦江之星(秦皇岛开发区高速路口店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I26" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2819,7 +2815,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2859,17 +2855,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7369458680036591656</t>
+          <t>6601186669309724675</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛卢龙县酒店）</t>
+          <t>7天酒店秦皇岛东北大学秦皇小巷店</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>锦江之星酒店(秦皇岛卢龙店)</t>
+          <t>7天连锁酒店(秦皇岛东北大学珠江道店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2895,13 +2891,13 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
@@ -2947,17 +2943,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7409962534867830824</t>
+          <t>7379862818146748457</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>锦江之星（秦皇岛山海关火车站店）</t>
+          <t>IU酒店(秦皇岛抚宁区新大集市场店)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛山海关火车站酒店)</t>
+          <t>iu酒店(抚宁新大集市场店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2969,7 +2965,7 @@
         <v>95</v>
       </c>
       <c r="I28" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2989,13 +2985,13 @@
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3028,24 +3024,20 @@
           <t>秦皇岛片区</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>秦皇岛市</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7598010588934506522</t>
+          <t>7555530999078062132</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>麗枫酒店（北戴河火车站环境工程学院店）</t>
+          <t>喆啡酒店（山海关火车站天下第一关古城店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>麗枫酒店(北戴河火车站环境工程学院店)</t>
+          <t>喆啡酒店(山海关火车站天下第一关古城店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3054,18 +3046,18 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>搭门店,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
         <v>10</v>
@@ -3083,7 +3075,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3123,33 +3115,33 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7331640626619877430</t>
+          <t>7369458680036591656</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（秦皇岛抚宁鸿莱大厦店）</t>
+          <t>锦江之星(秦皇岛卢龙县酒店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(秦皇岛抚宁鸿莱大厦店)</t>
+          <t>锦江之星酒店(秦皇岛卢龙店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3159,7 +3151,7 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
@@ -3171,7 +3163,7 @@
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3211,17 +3203,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7586507812433889323</t>
+          <t>7409962534867830824</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>锦江之星秦皇岛开发区植物园店</t>
+          <t>锦江之星（秦皇岛山海关火车站店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>锦江之星(开发区植物园店)</t>
+          <t>锦江之星(秦皇岛山海关火车站酒店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3230,14 +3222,14 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3247,13 +3239,13 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
@@ -3299,17 +3291,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6601141036154619912</t>
+          <t>7598010588934506522</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7天酒店（秦皇岛火车站店）</t>
+          <t>麗枫酒店（北戴河火车站环境工程学院店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7天酒店(秦皇岛火车站店)</t>
+          <t>麗枫酒店(北戴河火车站环境工程学院店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3318,30 +3310,30 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,提质量,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L32" t="n">
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N32" t="n">
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
@@ -3387,17 +3379,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6601149316914481165</t>
+          <t>7331640626619877430</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>锦江之星山海关火车站老龙头浴场酒店</t>
+          <t>维也纳国际酒店（秦皇岛抚宁鸿莱大厦店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛山海关火车站老龙头路浴场酒店)</t>
+          <t>维也纳国际酒店(秦皇岛抚宁鸿莱大厦店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3406,7 +3398,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3429,13 +3421,13 @@
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
@@ -3475,79 +3467,343 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
+          <t>7586507812433889323</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>锦江之星秦皇岛开发区植物园店</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>锦江之星(开发区植物园店)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>稳房源,拿收益</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>20</v>
+      </c>
+      <c r="N34" t="n">
+        <v>30</v>
+      </c>
+      <c r="O34" t="n">
+        <v>30</v>
+      </c>
+      <c r="P34" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>20</v>
+      </c>
+      <c r="R34" t="n">
+        <v>30</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="n">
+        <v>20</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>秦皇岛片区</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>秦皇岛市</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>6601141036154619912</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>7天酒店（秦皇岛火车站店）</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>7天酒店(秦皇岛火车站店)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>105</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>稳房源,拿收益</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="n">
+        <v>10</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N35" t="n">
+        <v>30</v>
+      </c>
+      <c r="O35" t="n">
+        <v>30</v>
+      </c>
+      <c r="P35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>20</v>
+      </c>
+      <c r="R35" t="n">
+        <v>30</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="n">
+        <v>20</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>秦皇岛片区</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>秦皇岛市</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>6601149316914481165</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>锦江之星山海关火车站老龙头浴场酒店</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>锦江之星(秦皇岛山海关火车站老龙头路浴场酒店)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>105</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>提质量,拿收益</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M36" t="n">
+        <v>30</v>
+      </c>
+      <c r="N36" t="n">
+        <v>30</v>
+      </c>
+      <c r="O36" t="n">
+        <v>20</v>
+      </c>
+      <c r="P36" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>25</v>
+      </c>
+      <c r="R36" t="n">
+        <v>30</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="n">
+        <v>20</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>秦皇岛片区</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>秦皇岛市</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
           <t>6601144610481784846</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>麗枫酒店秦皇岛火车站店</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>丽枫酒店(秦皇岛火车站店)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>已认证</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H37" t="n">
         <v>105</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I37" t="n">
         <v>5</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>提质量,拿收益</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" t="n">
-        <v>10</v>
-      </c>
-      <c r="M34" t="n">
-        <v>30</v>
-      </c>
-      <c r="N34" t="n">
-        <v>30</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" t="n">
+        <v>30</v>
+      </c>
+      <c r="N37" t="n">
+        <v>30</v>
+      </c>
+      <c r="O37" t="n">
         <v>25</v>
       </c>
-      <c r="P34" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>20</v>
-      </c>
-      <c r="R34" t="n">
-        <v>30</v>
-      </c>
-      <c r="S34" t="n">
-        <v>20</v>
-      </c>
-      <c r="T34" t="n">
-        <v>20</v>
-      </c>
-      <c r="U34" t="inlineStr">
+      <c r="P37" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>20</v>
+      </c>
+      <c r="R37" t="n">
+        <v>30</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="n">
+        <v>20</v>
+      </c>
+      <c r="U37" t="inlineStr">
         <is>
           <t>7249997748999555075</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>汇通百达网络科技（上海）有限公司</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V34"/>
-  <conditionalFormatting sqref="H2:H34">
+  <autoFilter ref="A1:V37"/>
+  <conditionalFormatting sqref="H2:H37">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3559,7 +3815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I34">
+  <conditionalFormatting sqref="I2:I37">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
